--- a/LF_study.xlsx
+++ b/LF_study.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL840"/>
+  <dimension ref="A1:AL867"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="18" max="18" width="20.7109375" style="2" customWidth="1"/>
@@ -80711,6 +80711,2462 @@
         </is>
       </c>
     </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="K841" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L841" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M841" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N841" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q841" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R841" s="2">
+        <v>46139</v>
+      </c>
+      <c r="S841" t="inlineStr">
+        <is>
+          <t>HELENA CUDJOE</t>
+        </is>
+      </c>
+      <c r="T841" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="U841" t="inlineStr">
+        <is>
+          <t>0539353913</t>
+        </is>
+      </c>
+      <c r="V841" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W841" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X841">
+        <v>27</v>
+      </c>
+      <c r="Y841" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z841" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA841" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB841" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD841" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL841" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>841</t>
+        </is>
+      </c>
+      <c r="K842" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L842" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M842" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N842" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q842" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R842" s="2">
+        <v>46139</v>
+      </c>
+      <c r="S842" t="inlineStr">
+        <is>
+          <t>HANNAH BAIDOO</t>
+        </is>
+      </c>
+      <c r="T842" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V842" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W842" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X842">
+        <v>16</v>
+      </c>
+      <c r="Y842" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z842" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA842" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB842" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD842" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL842" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>842</t>
+        </is>
+      </c>
+      <c r="K843" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L843" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M843" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N843" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q843" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R843" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S843" t="inlineStr">
+        <is>
+          <t>GRACE BUABENG</t>
+        </is>
+      </c>
+      <c r="T843" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V843" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W843" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X843">
+        <v>31</v>
+      </c>
+      <c r="Y843" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z843" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA843" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB843" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD843" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL843" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>843</t>
+        </is>
+      </c>
+      <c r="K844" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L844" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M844" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N844" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q844" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R844" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S844" t="inlineStr">
+        <is>
+          <t>DEBORAH AHINAKWA</t>
+        </is>
+      </c>
+      <c r="T844" t="inlineStr">
+        <is>
+          <t>DABIR</t>
+        </is>
+      </c>
+      <c r="V844" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W844" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X844">
+        <v>44</v>
+      </c>
+      <c r="Y844" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z844" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA844" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB844" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD844" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL844" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="K845" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L845" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M845" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N845" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q845" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R845" s="2">
+        <v>46141</v>
+      </c>
+      <c r="S845" t="inlineStr">
+        <is>
+          <t>STEVE ARTHUR</t>
+        </is>
+      </c>
+      <c r="T845" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V845" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W845" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X845">
+        <v>78</v>
+      </c>
+      <c r="Y845" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z845" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA845" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB845" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD845" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL845" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
+      </c>
+      <c r="K846" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L846" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M846" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N846" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q846" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R846" s="2">
+        <v>46142</v>
+      </c>
+      <c r="S846" t="inlineStr">
+        <is>
+          <t>MARY QUATSON</t>
+        </is>
+      </c>
+      <c r="T846" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V846" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W846" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X846">
+        <v>13</v>
+      </c>
+      <c r="Y846" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z846" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA846" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB846" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD846" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL846" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>846</t>
+        </is>
+      </c>
+      <c r="K847" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L847" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M847" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N847" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q847" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R847" s="2">
+        <v>46142</v>
+      </c>
+      <c r="S847" t="inlineStr">
+        <is>
+          <t>PRINCESS EKWAGO</t>
+        </is>
+      </c>
+      <c r="T847" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="U847" t="inlineStr">
+        <is>
+          <t>0247167063</t>
+        </is>
+      </c>
+      <c r="V847" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W847" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X847">
+        <v>13</v>
+      </c>
+      <c r="Y847" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z847" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA847" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB847" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD847" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL847" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>847</t>
+        </is>
+      </c>
+      <c r="K848" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L848" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M848" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N848" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q848" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R848" s="2">
+        <v>46145</v>
+      </c>
+      <c r="S848" t="inlineStr">
+        <is>
+          <t>ERIC ACKON</t>
+        </is>
+      </c>
+      <c r="T848" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V848" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W848" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X848">
+        <v>39</v>
+      </c>
+      <c r="Y848" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z848" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA848" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB848" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD848" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL848" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>848</t>
+        </is>
+      </c>
+      <c r="K849" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L849" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M849" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N849" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q849" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R849" s="2">
+        <v>46147</v>
+      </c>
+      <c r="S849" t="inlineStr">
+        <is>
+          <t>ANASTASIA QUAICOE</t>
+        </is>
+      </c>
+      <c r="T849" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="U849" t="inlineStr">
+        <is>
+          <t>0593122377</t>
+        </is>
+      </c>
+      <c r="V849" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W849" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X849">
+        <v>39</v>
+      </c>
+      <c r="Y849" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z849" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA849" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB849" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD849" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL849" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>849</t>
+        </is>
+      </c>
+      <c r="K850" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L850" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M850" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N850" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q850" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R850" s="2">
+        <v>46147</v>
+      </c>
+      <c r="S850" t="inlineStr">
+        <is>
+          <t>CHARITY MENSAH</t>
+        </is>
+      </c>
+      <c r="T850" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V850" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W850" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X850">
+        <v>14</v>
+      </c>
+      <c r="Y850" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z850" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA850" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB850" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD850" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL850" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>850</t>
+        </is>
+      </c>
+      <c r="K851" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L851" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M851" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N851" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q851" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R851" s="2">
+        <v>46147</v>
+      </c>
+      <c r="S851" t="inlineStr">
+        <is>
+          <t>ESTHER BAIDOO</t>
+        </is>
+      </c>
+      <c r="T851" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V851" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W851" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X851">
+        <v>77</v>
+      </c>
+      <c r="Y851" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z851" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA851" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB851" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD851" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL851" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>851</t>
+        </is>
+      </c>
+      <c r="K852" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L852" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M852" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N852" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q852" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R852" s="2">
+        <v>46148</v>
+      </c>
+      <c r="S852" t="inlineStr">
+        <is>
+          <t>ALBERT MANSO</t>
+        </is>
+      </c>
+      <c r="T852" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="U852" t="inlineStr">
+        <is>
+          <t>0207332460</t>
+        </is>
+      </c>
+      <c r="V852" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W852" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X852">
+        <v>74</v>
+      </c>
+      <c r="Y852" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z852" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA852" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB852" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD852" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL852" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>852</t>
+        </is>
+      </c>
+      <c r="K853" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L853" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M853" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N853" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q853" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R853" s="2">
+        <v>46148</v>
+      </c>
+      <c r="S853" t="inlineStr">
+        <is>
+          <t>AMA AMOEKU</t>
+        </is>
+      </c>
+      <c r="T853" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V853" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W853" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X853">
+        <v>46</v>
+      </c>
+      <c r="Y853" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z853" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA853" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB853" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD853" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL853" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>853</t>
+        </is>
+      </c>
+      <c r="K854" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L854" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M854" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N854" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q854" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R854" s="2">
+        <v>46149</v>
+      </c>
+      <c r="S854" t="inlineStr">
+        <is>
+          <t>EFUA DOMAH</t>
+        </is>
+      </c>
+      <c r="T854" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V854" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W854" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X854">
+        <v>86</v>
+      </c>
+      <c r="Y854" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z854" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA854" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB854" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD854" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL854" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>854</t>
+        </is>
+      </c>
+      <c r="K855" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L855" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M855" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N855" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q855" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R855" s="2">
+        <v>46150</v>
+      </c>
+      <c r="S855" t="inlineStr">
+        <is>
+          <t>CHRISTABEL A. DADZE</t>
+        </is>
+      </c>
+      <c r="T855" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="W855" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X855">
+        <v>19</v>
+      </c>
+      <c r="Y855" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z855" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA855" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB855" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD855" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL855" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>855</t>
+        </is>
+      </c>
+      <c r="K856" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L856" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M856" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N856" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q856" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R856" s="2">
+        <v>46150</v>
+      </c>
+      <c r="S856" t="inlineStr">
+        <is>
+          <t>MARY ESALWATI</t>
+        </is>
+      </c>
+      <c r="T856" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V856" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W856" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X856">
+        <v>16</v>
+      </c>
+      <c r="Y856" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z856" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA856" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB856" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD856" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL856" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>856</t>
+        </is>
+      </c>
+      <c r="K857" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L857" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M857" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N857" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q857" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R857" s="2">
+        <v>46150</v>
+      </c>
+      <c r="S857" t="inlineStr">
+        <is>
+          <t>GODWIN ANDOH</t>
+        </is>
+      </c>
+      <c r="T857" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V857" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W857" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X857">
+        <v>12</v>
+      </c>
+      <c r="Y857" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z857" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA857" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB857" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD857" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL857" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>857</t>
+        </is>
+      </c>
+      <c r="K858" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L858" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M858" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N858" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q858" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R858" s="2">
+        <v>46153</v>
+      </c>
+      <c r="S858" t="inlineStr">
+        <is>
+          <t>DORIS AKOSAH</t>
+        </is>
+      </c>
+      <c r="T858" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="U858" t="inlineStr">
+        <is>
+          <t>0549527470</t>
+        </is>
+      </c>
+      <c r="V858" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W858" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X858">
+        <v>48</v>
+      </c>
+      <c r="Y858" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z858" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA858" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB858" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD858" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL858" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>858</t>
+        </is>
+      </c>
+      <c r="K859" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L859" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M859" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N859" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q859" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R859" s="2">
+        <v>46124</v>
+      </c>
+      <c r="S859" t="inlineStr">
+        <is>
+          <t>MAAME EFUA SAAMAN</t>
+        </is>
+      </c>
+      <c r="T859" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V859" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W859" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X859">
+        <v>64</v>
+      </c>
+      <c r="Y859" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z859" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA859" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB859" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD859" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL859" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>859</t>
+        </is>
+      </c>
+      <c r="K860" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L860" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M860" t="inlineStr">
+        <is>
+          <t>Benyadzie CHPS</t>
+        </is>
+      </c>
+      <c r="N860" t="inlineStr">
+        <is>
+          <t>Benya</t>
+        </is>
+      </c>
+      <c r="Q860" t="inlineStr">
+        <is>
+          <t>THERESA MOORE</t>
+        </is>
+      </c>
+      <c r="R860" s="2">
+        <v>46155</v>
+      </c>
+      <c r="S860" t="inlineStr">
+        <is>
+          <t>COMFORT ODURO</t>
+        </is>
+      </c>
+      <c r="T860" t="inlineStr">
+        <is>
+          <t>BENYADZE</t>
+        </is>
+      </c>
+      <c r="V860" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W860" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X860">
+        <v>53</v>
+      </c>
+      <c r="Y860" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z860" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA860" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB860" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AD860" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL860" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>860</t>
+        </is>
+      </c>
+      <c r="K861" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L861" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M861" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N861" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q861" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R861" s="2">
+        <v>46101</v>
+      </c>
+      <c r="S861" t="inlineStr">
+        <is>
+          <t>KAF 01</t>
+        </is>
+      </c>
+      <c r="T861" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U861" t="inlineStr">
+        <is>
+          <t>0543025985</t>
+        </is>
+      </c>
+      <c r="V861" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W861" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X861">
+        <v>47</v>
+      </c>
+      <c r="Y861" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z861" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA861" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC861" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD861" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL861" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>861</t>
+        </is>
+      </c>
+      <c r="K862" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L862" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M862" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N862" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q862" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R862" s="2">
+        <v>46102</v>
+      </c>
+      <c r="S862" t="inlineStr">
+        <is>
+          <t>KAF 02</t>
+        </is>
+      </c>
+      <c r="T862" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U862" t="inlineStr">
+        <is>
+          <t>0541895105</t>
+        </is>
+      </c>
+      <c r="V862" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W862" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X862">
+        <v>70</v>
+      </c>
+      <c r="Y862" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z862" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA862" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB862" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC862" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD862" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL862" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>862</t>
+        </is>
+      </c>
+      <c r="K863" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L863" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M863" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N863" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q863" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R863" s="2">
+        <v>46108</v>
+      </c>
+      <c r="S863" t="inlineStr">
+        <is>
+          <t>KAF 03</t>
+        </is>
+      </c>
+      <c r="T863" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U863" t="inlineStr">
+        <is>
+          <t>0594144026</t>
+        </is>
+      </c>
+      <c r="V863" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W863" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X863">
+        <v>24</v>
+      </c>
+      <c r="Y863" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z863" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA863" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB863" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC863" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD863" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL863" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>863</t>
+        </is>
+      </c>
+      <c r="K864" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L864" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M864" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N864" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q864" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R864" s="2">
+        <v>46112</v>
+      </c>
+      <c r="S864" t="inlineStr">
+        <is>
+          <t>KAF 04</t>
+        </is>
+      </c>
+      <c r="T864" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U864" t="inlineStr">
+        <is>
+          <t>0241424931</t>
+        </is>
+      </c>
+      <c r="V864" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="W864" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X864">
+        <v>25</v>
+      </c>
+      <c r="Y864" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z864" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA864" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC864" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD864" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL864" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>864</t>
+        </is>
+      </c>
+      <c r="K865" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L865" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M865" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N865" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q865" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R865" s="2">
+        <v>46117</v>
+      </c>
+      <c r="S865" t="inlineStr">
+        <is>
+          <t>KAF 05</t>
+        </is>
+      </c>
+      <c r="T865" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U865" t="inlineStr">
+        <is>
+          <t>0544581726</t>
+        </is>
+      </c>
+      <c r="V865" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W865" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X865">
+        <v>17</v>
+      </c>
+      <c r="Y865" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z865" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA865" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB865" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC865" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD865" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL865" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>865</t>
+        </is>
+      </c>
+      <c r="K866" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L866" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M866" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N866" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q866" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R866" s="2">
+        <v>46120</v>
+      </c>
+      <c r="S866" t="inlineStr">
+        <is>
+          <t>KAF 06</t>
+        </is>
+      </c>
+      <c r="T866" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U866" t="inlineStr">
+        <is>
+          <t>0595537986</t>
+        </is>
+      </c>
+      <c r="V866" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W866" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X866">
+        <v>27</v>
+      </c>
+      <c r="Y866" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z866" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA866" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB866" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC866" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD866" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL866" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>866</t>
+        </is>
+      </c>
+      <c r="K867" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L867" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M867" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N867" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q867" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R867" s="2">
+        <v>46121</v>
+      </c>
+      <c r="S867" t="inlineStr">
+        <is>
+          <t>KAF 07</t>
+        </is>
+      </c>
+      <c r="T867" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U867" t="inlineStr">
+        <is>
+          <t>0542426669</t>
+        </is>
+      </c>
+      <c r="V867" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W867" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X867">
+        <v>13</v>
+      </c>
+      <c r="Y867" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z867" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA867" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB867" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC867" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD867" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL867" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LF_study.xlsx
+++ b/LF_study.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL867"/>
+  <dimension ref="A1:AL901"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="18" max="18" width="20.7109375" style="2" customWidth="1"/>
@@ -630,6 +630,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
       <c r="AC2" t="inlineStr">
         <is>
           <t>No</t>
@@ -1793,7 +1798,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -3801,7 +3806,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC35" t="inlineStr">
@@ -14806,6 +14811,11 @@
           <t>No</t>
         </is>
       </c>
+      <c r="W150" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
       <c r="AD150" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -27307,7 +27317,7 @@
       </c>
       <c r="AB283" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC283" t="inlineStr">
@@ -27317,7 +27327,7 @@
       </c>
       <c r="AD283" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="AL283" t="inlineStr">
@@ -83162,6 +83172,3280 @@
         </is>
       </c>
       <c r="AL867" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>867</t>
+        </is>
+      </c>
+      <c r="K868" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L868" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M868" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N868" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q868" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R868" s="2">
+        <v>46137</v>
+      </c>
+      <c r="S868" t="inlineStr">
+        <is>
+          <t>KAF 08</t>
+        </is>
+      </c>
+      <c r="T868" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U868" t="inlineStr">
+        <is>
+          <t>0240202017</t>
+        </is>
+      </c>
+      <c r="V868" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W868" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X868">
+        <v>67</v>
+      </c>
+      <c r="Y868" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z868" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA868" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB868" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC868" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD868" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL868" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="K869" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L869" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M869" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N869" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q869" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R869" s="2">
+        <v>46137</v>
+      </c>
+      <c r="S869" t="inlineStr">
+        <is>
+          <t>KAF 09</t>
+        </is>
+      </c>
+      <c r="T869" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U869" t="inlineStr">
+        <is>
+          <t>0549844705</t>
+        </is>
+      </c>
+      <c r="V869" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W869" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X869">
+        <v>7</v>
+      </c>
+      <c r="Y869" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z869" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA869" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB869" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC869" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD869" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL869" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>869</t>
+        </is>
+      </c>
+      <c r="K870" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L870" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M870" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N870" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q870" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R870" s="2">
+        <v>46137</v>
+      </c>
+      <c r="S870" t="inlineStr">
+        <is>
+          <t>KAF 10</t>
+        </is>
+      </c>
+      <c r="T870" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U870" t="inlineStr">
+        <is>
+          <t>0534614064</t>
+        </is>
+      </c>
+      <c r="V870" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W870" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X870">
+        <v>7</v>
+      </c>
+      <c r="Y870" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z870" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA870" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB870" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC870" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD870" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL870" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>870</t>
+        </is>
+      </c>
+      <c r="K871" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L871" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M871" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N871" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q871" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R871" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S871" t="inlineStr">
+        <is>
+          <t>KAF 11</t>
+        </is>
+      </c>
+      <c r="T871" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U871" t="inlineStr">
+        <is>
+          <t>0597351370</t>
+        </is>
+      </c>
+      <c r="V871" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W871" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X871">
+        <v>60</v>
+      </c>
+      <c r="Y871" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z871" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA871" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB871" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC871" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD871" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL871" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>871</t>
+        </is>
+      </c>
+      <c r="K872" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L872" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M872" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N872" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q872" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R872" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S872" t="inlineStr">
+        <is>
+          <t>KAF 12</t>
+        </is>
+      </c>
+      <c r="T872" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U872" t="inlineStr">
+        <is>
+          <t>0256212802</t>
+        </is>
+      </c>
+      <c r="V872" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W872" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X872">
+        <v>25</v>
+      </c>
+      <c r="Y872" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z872" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA872" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB872" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC872" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD872" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL872" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>872</t>
+        </is>
+      </c>
+      <c r="K873" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L873" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M873" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N873" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q873" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R873" s="2">
+        <v>46143</v>
+      </c>
+      <c r="S873" t="inlineStr">
+        <is>
+          <t>KAF 13</t>
+        </is>
+      </c>
+      <c r="T873" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="V873" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W873" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X873">
+        <v>45</v>
+      </c>
+      <c r="Y873" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z873" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA873" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB873" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC873" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD873" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL873" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>873</t>
+        </is>
+      </c>
+      <c r="K874" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L874" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M874" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N874" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q874" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R874" s="2">
+        <v>46145</v>
+      </c>
+      <c r="S874" t="inlineStr">
+        <is>
+          <t>KAF 14</t>
+        </is>
+      </c>
+      <c r="T874" t="inlineStr">
+        <is>
+          <t>ABROBIAN0</t>
+        </is>
+      </c>
+      <c r="U874" t="inlineStr">
+        <is>
+          <t>0271885068</t>
+        </is>
+      </c>
+      <c r="V874" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W874" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X874">
+        <v>24</v>
+      </c>
+      <c r="Y874" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z874" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA874" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB874" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC874" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD874" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL874" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>874</t>
+        </is>
+      </c>
+      <c r="K875" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L875" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M875" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N875" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q875" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R875" s="2">
+        <v>46150</v>
+      </c>
+      <c r="S875" t="inlineStr">
+        <is>
+          <t>KAF 15</t>
+        </is>
+      </c>
+      <c r="T875" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U875" t="inlineStr">
+        <is>
+          <t>0547268021</t>
+        </is>
+      </c>
+      <c r="V875" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W875" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X875">
+        <v>34</v>
+      </c>
+      <c r="Y875" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z875" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA875" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB875" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC875" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD875" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL875" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>875</t>
+        </is>
+      </c>
+      <c r="K876" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L876" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M876" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N876" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q876" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R876" s="2">
+        <v>46151</v>
+      </c>
+      <c r="S876" t="inlineStr">
+        <is>
+          <t>KAF 16</t>
+        </is>
+      </c>
+      <c r="T876" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U876" t="inlineStr">
+        <is>
+          <t>0546319192</t>
+        </is>
+      </c>
+      <c r="V876" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W876" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X876">
+        <v>38</v>
+      </c>
+      <c r="Y876" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z876" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA876" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB876" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC876" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD876" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL876" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>876</t>
+        </is>
+      </c>
+      <c r="K877" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L877" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M877" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N877" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q877" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R877" s="2">
+        <v>46151</v>
+      </c>
+      <c r="S877" t="inlineStr">
+        <is>
+          <t>KAF 17</t>
+        </is>
+      </c>
+      <c r="T877" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U877" t="inlineStr">
+        <is>
+          <t>0548386488</t>
+        </is>
+      </c>
+      <c r="V877" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W877" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X877">
+        <v>15</v>
+      </c>
+      <c r="Y877" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z877" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA877" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB877" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC877" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD877" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL877" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>877</t>
+        </is>
+      </c>
+      <c r="K878" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L878" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M878" t="inlineStr">
+        <is>
+          <t>Kafodzidzi CHPS</t>
+        </is>
+      </c>
+      <c r="N878" t="inlineStr">
+        <is>
+          <t>Kafodzidzi</t>
+        </is>
+      </c>
+      <c r="Q878" t="inlineStr">
+        <is>
+          <t>Rejoice Tsifokor</t>
+        </is>
+      </c>
+      <c r="R878" s="2">
+        <v>46152</v>
+      </c>
+      <c r="S878" t="inlineStr">
+        <is>
+          <t>KAF 18</t>
+        </is>
+      </c>
+      <c r="T878" t="inlineStr">
+        <is>
+          <t>KAFODZIDZI</t>
+        </is>
+      </c>
+      <c r="U878" t="inlineStr">
+        <is>
+          <t>0555386232</t>
+        </is>
+      </c>
+      <c r="V878" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W878" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X878">
+        <v>14</v>
+      </c>
+      <c r="Y878" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z878" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA878" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB878" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AC878" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD878" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL878" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>878</t>
+        </is>
+      </c>
+      <c r="K879" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L879" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M879" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N879" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q879" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R879" s="2">
+        <v>46109</v>
+      </c>
+      <c r="S879" t="inlineStr">
+        <is>
+          <t>AMP 01</t>
+        </is>
+      </c>
+      <c r="T879" t="inlineStr">
+        <is>
+          <t>AKYINIM</t>
+        </is>
+      </c>
+      <c r="U879" t="inlineStr">
+        <is>
+          <t>BA-62</t>
+        </is>
+      </c>
+      <c r="V879" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W879" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X879">
+        <v>11</v>
+      </c>
+      <c r="Y879" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z879" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA879" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB879" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC879" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD879" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL879" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>879</t>
+        </is>
+      </c>
+      <c r="K880" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L880" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M880" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N880" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q880" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R880" s="2">
+        <v>46109</v>
+      </c>
+      <c r="S880" t="inlineStr">
+        <is>
+          <t>AMP 02</t>
+        </is>
+      </c>
+      <c r="T880" t="inlineStr">
+        <is>
+          <t>AKYINIM</t>
+        </is>
+      </c>
+      <c r="U880" t="inlineStr">
+        <is>
+          <t>BA-62</t>
+        </is>
+      </c>
+      <c r="V880" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W880" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X880">
+        <v>12</v>
+      </c>
+      <c r="Y880" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z880" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA880" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB880" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC880" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD880" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL880" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>880</t>
+        </is>
+      </c>
+      <c r="K881" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L881" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M881" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N881" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q881" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R881" s="2">
+        <v>46109</v>
+      </c>
+      <c r="S881" t="inlineStr">
+        <is>
+          <t>AMP 03</t>
+        </is>
+      </c>
+      <c r="T881" t="inlineStr">
+        <is>
+          <t>AMPENYI</t>
+        </is>
+      </c>
+      <c r="U881" t="inlineStr">
+        <is>
+          <t>AM-121</t>
+        </is>
+      </c>
+      <c r="V881" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W881" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X881">
+        <v>5</v>
+      </c>
+      <c r="Y881" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z881" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA881" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB881" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC881" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD881" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL881" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>881</t>
+        </is>
+      </c>
+      <c r="K882" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L882" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M882" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N882" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q882" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R882" s="2">
+        <v>46109</v>
+      </c>
+      <c r="S882" t="inlineStr">
+        <is>
+          <t>AMP 04</t>
+        </is>
+      </c>
+      <c r="T882" t="inlineStr">
+        <is>
+          <t>AMPENYI</t>
+        </is>
+      </c>
+      <c r="U882" t="inlineStr">
+        <is>
+          <t>AP-68</t>
+        </is>
+      </c>
+      <c r="V882" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W882" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X882">
+        <v>6</v>
+      </c>
+      <c r="Y882" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z882" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA882" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB882" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC882" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD882" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL882" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>882</t>
+        </is>
+      </c>
+      <c r="K883" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L883" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M883" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N883" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q883" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R883" s="2">
+        <v>46109</v>
+      </c>
+      <c r="S883" t="inlineStr">
+        <is>
+          <t>AMP 05</t>
+        </is>
+      </c>
+      <c r="T883" t="inlineStr">
+        <is>
+          <t>DABIR</t>
+        </is>
+      </c>
+      <c r="V883" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W883" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X883">
+        <v>36</v>
+      </c>
+      <c r="Y883" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z883" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA883" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB883" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC883" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD883" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL883" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>883</t>
+        </is>
+      </c>
+      <c r="K884" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L884" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M884" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N884" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q884" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R884" s="2">
+        <v>46109</v>
+      </c>
+      <c r="S884" t="inlineStr">
+        <is>
+          <t>AMP 06</t>
+        </is>
+      </c>
+      <c r="T884" t="inlineStr">
+        <is>
+          <t>BRENU AKYINIM</t>
+        </is>
+      </c>
+      <c r="U884" t="inlineStr">
+        <is>
+          <t>BA-016</t>
+        </is>
+      </c>
+      <c r="V884" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W884" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X884">
+        <v>5</v>
+      </c>
+      <c r="Y884" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z884" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA884" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB884" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC884" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD884" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL884" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>884</t>
+        </is>
+      </c>
+      <c r="K885" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L885" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M885" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N885" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q885" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R885" s="2">
+        <v>46110</v>
+      </c>
+      <c r="S885" t="inlineStr">
+        <is>
+          <t>AMP 07</t>
+        </is>
+      </c>
+      <c r="T885" t="inlineStr">
+        <is>
+          <t>AYENSUDO</t>
+        </is>
+      </c>
+      <c r="U885" t="inlineStr">
+        <is>
+          <t>AY-346</t>
+        </is>
+      </c>
+      <c r="V885" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W885" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X885">
+        <v>11</v>
+      </c>
+      <c r="Y885" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z885" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA885" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB885" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC885" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD885" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL885" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>885</t>
+        </is>
+      </c>
+      <c r="K886" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L886" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M886" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N886" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q886" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R886" s="2">
+        <v>46135</v>
+      </c>
+      <c r="S886" t="inlineStr">
+        <is>
+          <t>AMP 08</t>
+        </is>
+      </c>
+      <c r="T886" t="inlineStr">
+        <is>
+          <t>AMPENYI</t>
+        </is>
+      </c>
+      <c r="U886" t="inlineStr">
+        <is>
+          <t>AP-178</t>
+        </is>
+      </c>
+      <c r="V886" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W886" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X886">
+        <v>18</v>
+      </c>
+      <c r="Y886" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z886" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA886" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB886" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC886" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD886" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL886" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>886</t>
+        </is>
+      </c>
+      <c r="K887" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L887" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M887" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N887" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q887" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R887" s="2">
+        <v>46136</v>
+      </c>
+      <c r="S887" t="inlineStr">
+        <is>
+          <t>AMP 09</t>
+        </is>
+      </c>
+      <c r="T887" t="inlineStr">
+        <is>
+          <t>AYENSUDO</t>
+        </is>
+      </c>
+      <c r="U887" t="inlineStr">
+        <is>
+          <t>AY-61</t>
+        </is>
+      </c>
+      <c r="V887" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W887" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X887">
+        <v>52</v>
+      </c>
+      <c r="Y887" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z887" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA887" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB887" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC887" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD887" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL887" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>887</t>
+        </is>
+      </c>
+      <c r="K888" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L888" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M888" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N888" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q888" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R888" s="2">
+        <v>46137</v>
+      </c>
+      <c r="S888" t="inlineStr">
+        <is>
+          <t>AMP 10</t>
+        </is>
+      </c>
+      <c r="T888" t="inlineStr">
+        <is>
+          <t>AYENSUDO</t>
+        </is>
+      </c>
+      <c r="U888" t="inlineStr">
+        <is>
+          <t>AY-48</t>
+        </is>
+      </c>
+      <c r="V888" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W888" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X888">
+        <v>84</v>
+      </c>
+      <c r="Y888" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z888" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA888" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB888" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC888" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD888" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL888" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>888</t>
+        </is>
+      </c>
+      <c r="K889" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L889" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M889" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N889" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q889" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R889" s="2">
+        <v>46137</v>
+      </c>
+      <c r="S889" t="inlineStr">
+        <is>
+          <t>AMP 11</t>
+        </is>
+      </c>
+      <c r="T889" t="inlineStr">
+        <is>
+          <t>AYENSUDO</t>
+        </is>
+      </c>
+      <c r="U889" t="inlineStr">
+        <is>
+          <t>AY-70</t>
+        </is>
+      </c>
+      <c r="V889" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W889" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X889">
+        <v>10</v>
+      </c>
+      <c r="Y889" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z889" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA889" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB889" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC889" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD889" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL889" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>889</t>
+        </is>
+      </c>
+      <c r="K890" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L890" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M890" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N890" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q890" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R890" s="2">
+        <v>46139</v>
+      </c>
+      <c r="S890" t="inlineStr">
+        <is>
+          <t>AMP 12</t>
+        </is>
+      </c>
+      <c r="T890" t="inlineStr">
+        <is>
+          <t>BRENU AKYINIM</t>
+        </is>
+      </c>
+      <c r="V890" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W890" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X890">
+        <v>27</v>
+      </c>
+      <c r="Y890" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z890" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA890" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB890" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC890" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD890" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL890" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>890</t>
+        </is>
+      </c>
+      <c r="K891" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L891" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M891" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N891" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q891" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R891" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S891" t="inlineStr">
+        <is>
+          <t>AMP 13</t>
+        </is>
+      </c>
+      <c r="T891" t="inlineStr">
+        <is>
+          <t>AYENSUDO</t>
+        </is>
+      </c>
+      <c r="V891" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W891" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X891">
+        <v>14</v>
+      </c>
+      <c r="Y891" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z891" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA891" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB891" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC891" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD891" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL891" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>891</t>
+        </is>
+      </c>
+      <c r="K892" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L892" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M892" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N892" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q892" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R892" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S892" t="inlineStr">
+        <is>
+          <t>AMP 14</t>
+        </is>
+      </c>
+      <c r="V892" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Y892" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z892" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA892" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB892" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC892" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD892" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL892" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>892</t>
+        </is>
+      </c>
+      <c r="K893" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L893" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M893" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N893" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q893" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R893" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S893" t="inlineStr">
+        <is>
+          <t>AMP 15</t>
+        </is>
+      </c>
+      <c r="T893" t="inlineStr">
+        <is>
+          <t>AYENSUDO</t>
+        </is>
+      </c>
+      <c r="V893" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W893" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X893">
+        <v>16</v>
+      </c>
+      <c r="Y893" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z893" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA893" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB893" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC893" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD893" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL893" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>893</t>
+        </is>
+      </c>
+      <c r="K894" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L894" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M894" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N894" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q894" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R894" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S894" t="inlineStr">
+        <is>
+          <t>AMP 16</t>
+        </is>
+      </c>
+      <c r="T894" t="inlineStr">
+        <is>
+          <t>AYENSUDO</t>
+        </is>
+      </c>
+      <c r="U894" t="inlineStr">
+        <is>
+          <t>059110505</t>
+        </is>
+      </c>
+      <c r="V894" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W894" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X894">
+        <v>18</v>
+      </c>
+      <c r="Y894" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z894" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA894" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB894" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC894" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD894" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL894" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>894</t>
+        </is>
+      </c>
+      <c r="K895" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L895" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M895" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N895" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q895" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R895" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S895" t="inlineStr">
+        <is>
+          <t>AMP 17</t>
+        </is>
+      </c>
+      <c r="T895" t="inlineStr">
+        <is>
+          <t>AMPENYI</t>
+        </is>
+      </c>
+      <c r="V895" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W895" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X895">
+        <v>13</v>
+      </c>
+      <c r="Y895" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z895" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA895" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB895" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC895" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD895" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL895" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>895</t>
+        </is>
+      </c>
+      <c r="K896" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L896" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M896" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N896" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q896" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R896" s="2">
+        <v>46141</v>
+      </c>
+      <c r="S896" t="inlineStr">
+        <is>
+          <t>AMP 18</t>
+        </is>
+      </c>
+      <c r="T896" t="inlineStr">
+        <is>
+          <t>AMPENYI</t>
+        </is>
+      </c>
+      <c r="U896" t="inlineStr">
+        <is>
+          <t>0544038157</t>
+        </is>
+      </c>
+      <c r="V896" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W896" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X896">
+        <v>12</v>
+      </c>
+      <c r="Y896" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z896" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA896" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB896" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC896" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD896" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL896" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>896</t>
+        </is>
+      </c>
+      <c r="K897" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L897" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M897" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N897" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q897" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R897" s="2">
+        <v>46137</v>
+      </c>
+      <c r="S897" t="inlineStr">
+        <is>
+          <t>AMP 19</t>
+        </is>
+      </c>
+      <c r="T897" t="inlineStr">
+        <is>
+          <t>AMPENYI</t>
+        </is>
+      </c>
+      <c r="U897" t="inlineStr">
+        <is>
+          <t>0544038157</t>
+        </is>
+      </c>
+      <c r="V897" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W897" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X897">
+        <v>12</v>
+      </c>
+      <c r="Y897" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z897" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA897" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB897" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC897" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD897" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL897" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>897</t>
+        </is>
+      </c>
+      <c r="K898" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L898" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M898" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N898" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q898" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R898" s="2">
+        <v>46143</v>
+      </c>
+      <c r="S898" t="inlineStr">
+        <is>
+          <t>AMP 20</t>
+        </is>
+      </c>
+      <c r="T898" t="inlineStr">
+        <is>
+          <t>AMPENYI</t>
+        </is>
+      </c>
+      <c r="V898" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W898" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X898">
+        <v>30</v>
+      </c>
+      <c r="Y898" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z898" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA898" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB898" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC898" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD898" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL898" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>898</t>
+        </is>
+      </c>
+      <c r="K899" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L899" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M899" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N899" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q899" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R899" s="2">
+        <v>46144</v>
+      </c>
+      <c r="S899" t="inlineStr">
+        <is>
+          <t>AMP 21</t>
+        </is>
+      </c>
+      <c r="T899" t="inlineStr">
+        <is>
+          <t>AMPENYI</t>
+        </is>
+      </c>
+      <c r="V899" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W899" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X899">
+        <v>33</v>
+      </c>
+      <c r="Y899" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z899" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA899" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB899" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC899" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD899" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL899" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>899</t>
+        </is>
+      </c>
+      <c r="K900" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L900" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M900" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N900" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q900" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R900" s="2">
+        <v>46145</v>
+      </c>
+      <c r="S900" t="inlineStr">
+        <is>
+          <t>AMP 22</t>
+        </is>
+      </c>
+      <c r="T900" t="inlineStr">
+        <is>
+          <t>AMPENYI</t>
+        </is>
+      </c>
+      <c r="U900" t="inlineStr">
+        <is>
+          <t>AM-148</t>
+        </is>
+      </c>
+      <c r="V900" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W900" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X900">
+        <v>32</v>
+      </c>
+      <c r="Y900" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z900" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA900" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB900" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC900" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD900" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL900" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>900</t>
+        </is>
+      </c>
+      <c r="K901" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L901" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M901" t="inlineStr">
+        <is>
+          <t>Ampenyi CHPS</t>
+        </is>
+      </c>
+      <c r="N901" t="inlineStr">
+        <is>
+          <t>Ampenyi</t>
+        </is>
+      </c>
+      <c r="Q901" t="inlineStr">
+        <is>
+          <t>Gloria Arthur Asabre</t>
+        </is>
+      </c>
+      <c r="R901" s="2">
+        <v>46149</v>
+      </c>
+      <c r="S901" t="inlineStr">
+        <is>
+          <t>AMP 23</t>
+        </is>
+      </c>
+      <c r="T901" t="inlineStr">
+        <is>
+          <t>AYENSUDO</t>
+        </is>
+      </c>
+      <c r="U901" t="inlineStr">
+        <is>
+          <t>AY-103</t>
+        </is>
+      </c>
+      <c r="V901" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W901" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X901">
+        <v>28</v>
+      </c>
+      <c r="Y901" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z901" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA901" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB901" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC901" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD901" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL901" t="inlineStr">
         <is>
           <t>Incomplete</t>
         </is>

--- a/LF_study.xlsx
+++ b/LF_study.xlsx
@@ -1808,7 +1808,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
@@ -4286,7 +4286,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
@@ -4296,7 +4296,7 @@
       </c>
       <c r="AD40" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="AL40" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
@@ -4585,7 +4585,7 @@
       </c>
       <c r="AD43" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="AL43" t="inlineStr">
@@ -4864,7 +4864,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="AD46" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="AL46" t="inlineStr">
@@ -4962,7 +4962,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
@@ -4972,7 +4972,7 @@
       </c>
       <c r="AD47" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="AL47" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
@@ -5070,7 +5070,7 @@
       </c>
       <c r="AD48" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="AL48" t="inlineStr">
@@ -5638,17 +5638,17 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
       <c r="AD54" t="inlineStr">
         <is>
-          <t>Incomplete</t>
+          <t>Complete</t>
         </is>
       </c>
       <c r="AL54" t="inlineStr">
@@ -6523,6 +6523,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD63" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -9812,6 +9817,11 @@
           <t>0548337201</t>
         </is>
       </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W97" t="inlineStr">
         <is>
           <t>Female</t>
@@ -9998,6 +10008,11 @@
           <t>KOKWADO</t>
         </is>
       </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W99" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10091,6 +10106,11 @@
           <t>0547986117</t>
         </is>
       </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W100" t="inlineStr">
         <is>
           <t>Male</t>
@@ -10184,6 +10204,11 @@
           <t>0557663805</t>
         </is>
       </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W101" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10277,6 +10302,11 @@
           <t>0591354804</t>
         </is>
       </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W102" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10370,6 +10400,11 @@
           <t>0535656196</t>
         </is>
       </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W103" t="inlineStr">
         <is>
           <t>Male</t>
@@ -10463,6 +10498,11 @@
           <t>0591190055</t>
         </is>
       </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W104" t="inlineStr">
         <is>
           <t>Male</t>
@@ -10556,6 +10596,11 @@
           <t>055442291</t>
         </is>
       </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W105" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10649,6 +10694,11 @@
           <t>0243831208</t>
         </is>
       </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W106" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10742,6 +10792,11 @@
           <t>024224994</t>
         </is>
       </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W107" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10835,6 +10890,11 @@
           <t>0592397244</t>
         </is>
       </c>
+      <c r="V108" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W108" t="inlineStr">
         <is>
           <t>Female</t>
@@ -10928,6 +10988,11 @@
           <t>0242981385</t>
         </is>
       </c>
+      <c r="V109" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W109" t="inlineStr">
         <is>
           <t>Female</t>
@@ -11021,6 +11086,11 @@
           <t>0240629144</t>
         </is>
       </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W110" t="inlineStr">
         <is>
           <t>Male</t>
@@ -11114,6 +11184,11 @@
           <t>0241931517</t>
         </is>
       </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W111" t="inlineStr">
         <is>
           <t>Female</t>
@@ -11207,6 +11282,11 @@
           <t>0502471961</t>
         </is>
       </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W112" t="inlineStr">
         <is>
           <t>Female</t>
@@ -11295,6 +11375,11 @@
           <t>BRENU AKYINIM</t>
         </is>
       </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W113" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12167,6 +12252,11 @@
           <t>BA134/80</t>
         </is>
       </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W122" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12260,6 +12350,11 @@
           <t>0242235085</t>
         </is>
       </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W123" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12348,6 +12443,11 @@
           <t>BRENU AKYINIM</t>
         </is>
       </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W124" t="inlineStr">
         <is>
           <t>Male</t>
@@ -12441,6 +12541,11 @@
           <t>054690481</t>
         </is>
       </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W125" t="inlineStr">
         <is>
           <t>Female</t>
@@ -12529,6 +12634,11 @@
           <t>BRENU AKYINIM</t>
         </is>
       </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W126" t="inlineStr">
         <is>
           <t>Female</t>
@@ -14012,6 +14122,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD141" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14100,6 +14215,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD142" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14193,6 +14313,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD143" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14286,6 +14411,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC144" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD144" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14379,6 +14509,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD145" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14472,6 +14607,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC146" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD146" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14565,6 +14705,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD147" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14658,6 +14803,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC148" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD148" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14751,6 +14901,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD149" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14816,6 +14971,21 @@
           <t>Female</t>
         </is>
       </c>
+      <c r="Y150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD150" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14909,6 +15079,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD151" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -14997,6 +15172,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD152" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15085,6 +15265,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD153" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15173,6 +15358,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC154" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD154" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15261,6 +15451,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD155" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15354,6 +15549,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD156" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15442,6 +15642,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD157" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15530,6 +15735,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD158" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15623,6 +15833,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD159" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15716,6 +15931,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD160" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15804,6 +16024,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD161" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15897,6 +16122,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD162" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -15985,6 +16215,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD163" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -16073,6 +16308,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD164" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -16161,6 +16401,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC165" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD165" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -18548,6 +18793,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC190" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD190" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -18641,6 +18891,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC191" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD191" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -18734,6 +18989,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC192" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD192" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -18827,6 +19087,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC193" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD193" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -18920,6 +19185,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC194" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD194" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -19008,6 +19278,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC195" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD195" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -19101,6 +19376,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC196" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD196" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -19189,6 +19469,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC197" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD197" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -19282,6 +19567,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC198" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD198" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -19468,6 +19758,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC200" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD200" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -20860,6 +21155,11 @@
           <t>0554961363</t>
         </is>
       </c>
+      <c r="V215" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W215" t="inlineStr">
         <is>
           <t>Male</t>
@@ -21224,6 +21524,11 @@
           <t xml:space="preserve">ATONKWA </t>
         </is>
       </c>
+      <c r="V219" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W219" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21312,6 +21617,11 @@
           <t xml:space="preserve">ATONKWA </t>
         </is>
       </c>
+      <c r="V220" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W220" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21400,6 +21710,11 @@
           <t xml:space="preserve">ATONKWA </t>
         </is>
       </c>
+      <c r="V221" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W221" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21488,6 +21803,11 @@
           <t xml:space="preserve">ATONKWA </t>
         </is>
       </c>
+      <c r="V222" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W222" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21576,6 +21896,11 @@
           <t xml:space="preserve">ATONKWA </t>
         </is>
       </c>
+      <c r="V223" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W223" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21669,6 +21994,11 @@
           <t>0246793512</t>
         </is>
       </c>
+      <c r="V224" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W224" t="inlineStr">
         <is>
           <t>Male</t>
@@ -21757,6 +22087,11 @@
           <t>ABINA</t>
         </is>
       </c>
+      <c r="V225" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W225" t="inlineStr">
         <is>
           <t>Female</t>
@@ -21845,6 +22180,11 @@
           <t>KOFUL</t>
         </is>
       </c>
+      <c r="V226" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W226" t="inlineStr">
         <is>
           <t>Male</t>
@@ -21933,6 +22273,11 @@
           <t>KOFUL</t>
         </is>
       </c>
+      <c r="V227" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W227" t="inlineStr">
         <is>
           <t>Male</t>
@@ -22021,6 +22366,11 @@
           <t xml:space="preserve">ATONKWA </t>
         </is>
       </c>
+      <c r="V228" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W228" t="inlineStr">
         <is>
           <t>Female</t>
@@ -22114,6 +22464,11 @@
           <t>0530766807</t>
         </is>
       </c>
+      <c r="V229" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W229" t="inlineStr">
         <is>
           <t>Male</t>
@@ -22202,6 +22557,11 @@
           <t xml:space="preserve">ATONKWA </t>
         </is>
       </c>
+      <c r="V230" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W230" t="inlineStr">
         <is>
           <t>Female</t>
@@ -22287,6 +22647,11 @@
           <t>KOFUL</t>
         </is>
       </c>
+      <c r="V231" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W231" t="inlineStr">
         <is>
           <t>Male</t>
@@ -22375,6 +22740,11 @@
           <t xml:space="preserve">ATONKWA </t>
         </is>
       </c>
+      <c r="V232" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W232" t="inlineStr">
         <is>
           <t>Female</t>
@@ -22463,6 +22833,11 @@
           <t xml:space="preserve">ATONKWA </t>
         </is>
       </c>
+      <c r="V233" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W233" t="inlineStr">
         <is>
           <t>Female</t>
@@ -22551,6 +22926,11 @@
           <t xml:space="preserve">ATONKWA </t>
         </is>
       </c>
+      <c r="V234" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W234" t="inlineStr">
         <is>
           <t>Male</t>
@@ -24596,6 +24976,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC255" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD255" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -27292,6 +27677,11 @@
           <t>0244499063</t>
         </is>
       </c>
+      <c r="V283" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W283" t="inlineStr">
         <is>
           <t>Male</t>
@@ -28649,6 +29039,11 @@
           <t>0551478177</t>
         </is>
       </c>
+      <c r="V297" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W297" t="inlineStr">
         <is>
           <t>Male</t>
@@ -29098,12 +29493,12 @@
       </c>
       <c r="O302" t="inlineStr">
         <is>
-          <t>Kokofu CHPS</t>
+          <t>Anteadze/ Odumase CHPS</t>
         </is>
       </c>
       <c r="P302" t="inlineStr">
         <is>
-          <t>Kokofu</t>
+          <t>Anteadze</t>
         </is>
       </c>
       <c r="Q302" t="inlineStr">
@@ -29387,12 +29782,12 @@
       </c>
       <c r="O305" t="inlineStr">
         <is>
-          <t>Sampa CHPS</t>
+          <t>Anteadze/ Odumase CHPS</t>
         </is>
       </c>
       <c r="P305" t="inlineStr">
         <is>
-          <t>Sampa</t>
+          <t>Anteadze</t>
         </is>
       </c>
       <c r="Q305" t="inlineStr">
@@ -29477,12 +29872,12 @@
       </c>
       <c r="O306" t="inlineStr">
         <is>
-          <t>Sampa CHPS</t>
+          <t>Anteadze/ Odumase CHPS</t>
         </is>
       </c>
       <c r="P306" t="inlineStr">
         <is>
-          <t>Sampa</t>
+          <t>Anteadze</t>
         </is>
       </c>
       <c r="Q306" t="inlineStr">
@@ -29655,12 +30050,12 @@
       </c>
       <c r="O308" t="inlineStr">
         <is>
-          <t>Sampa CHPS</t>
+          <t>Anteadze/ Odumase CHPS</t>
         </is>
       </c>
       <c r="P308" t="inlineStr">
         <is>
-          <t>Sampa</t>
+          <t>Anteadze</t>
         </is>
       </c>
       <c r="Q308" t="inlineStr">
@@ -29753,12 +30148,12 @@
       </c>
       <c r="O309" t="inlineStr">
         <is>
-          <t>Sampa CHPS</t>
+          <t>Anteadze/ Odumase CHPS</t>
         </is>
       </c>
       <c r="P309" t="inlineStr">
         <is>
-          <t>Sampa</t>
+          <t>Anteadze</t>
         </is>
       </c>
       <c r="Q309" t="inlineStr">
@@ -29851,12 +30246,12 @@
       </c>
       <c r="O310" t="inlineStr">
         <is>
-          <t>Sampa CHPS</t>
+          <t>Anteadze/ Odumase CHPS</t>
         </is>
       </c>
       <c r="P310" t="inlineStr">
         <is>
-          <t>Sampa</t>
+          <t>Anteadze</t>
         </is>
       </c>
       <c r="Q310" t="inlineStr">
@@ -29944,12 +30339,12 @@
       </c>
       <c r="O311" t="inlineStr">
         <is>
-          <t>Sampa CHPS</t>
+          <t>Anteadze/ Odumase CHPS</t>
         </is>
       </c>
       <c r="P311" t="inlineStr">
         <is>
-          <t>Sampa</t>
+          <t>Anteadze</t>
         </is>
       </c>
       <c r="Q311" t="inlineStr">
@@ -30037,12 +30432,12 @@
       </c>
       <c r="O312" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P312" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q312" t="inlineStr">
@@ -30135,12 +30530,12 @@
       </c>
       <c r="O313" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P313" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q313" t="inlineStr">
@@ -30233,12 +30628,12 @@
       </c>
       <c r="O314" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P314" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q314" t="inlineStr">
@@ -30326,12 +30721,12 @@
       </c>
       <c r="O315" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P315" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q315" t="inlineStr">
@@ -30424,12 +30819,12 @@
       </c>
       <c r="O316" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P316" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q316" t="inlineStr">
@@ -30522,12 +30917,12 @@
       </c>
       <c r="O317" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P317" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q317" t="inlineStr">
@@ -30620,12 +31015,12 @@
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P318" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q318" t="inlineStr">
@@ -30718,12 +31113,12 @@
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P319" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q319" t="inlineStr">
@@ -30816,12 +31211,12 @@
       </c>
       <c r="O320" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P320" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q320" t="inlineStr">
@@ -30914,12 +31309,12 @@
       </c>
       <c r="O321" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P321" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q321" t="inlineStr">
@@ -31012,12 +31407,12 @@
       </c>
       <c r="O322" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P322" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q322" t="inlineStr">
@@ -31110,12 +31505,12 @@
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P323" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q323" t="inlineStr">
@@ -31208,12 +31603,12 @@
       </c>
       <c r="O324" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P324" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q324" t="inlineStr">
@@ -31306,12 +31701,12 @@
       </c>
       <c r="O325" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P325" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q325" t="inlineStr">
@@ -31404,12 +31799,12 @@
       </c>
       <c r="O326" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P326" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q326" t="inlineStr">
@@ -31502,12 +31897,12 @@
       </c>
       <c r="O327" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P327" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q327" t="inlineStr">
@@ -31600,12 +31995,12 @@
       </c>
       <c r="O328" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P328" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q328" t="inlineStr">
@@ -31698,12 +32093,12 @@
       </c>
       <c r="O329" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P329" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q329" t="inlineStr">
@@ -31796,12 +32191,12 @@
       </c>
       <c r="O330" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P330" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q330" t="inlineStr">
@@ -31889,12 +32284,12 @@
       </c>
       <c r="O331" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P331" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q331" t="inlineStr">
@@ -31982,12 +32377,12 @@
       </c>
       <c r="O332" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P332" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q332" t="inlineStr">
@@ -32075,12 +32470,12 @@
       </c>
       <c r="O333" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P333" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q333" t="inlineStr">
@@ -32168,12 +32563,12 @@
       </c>
       <c r="O334" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P334" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q334" t="inlineStr">
@@ -32261,12 +32656,12 @@
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P335" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q335" t="inlineStr">
@@ -32354,12 +32749,12 @@
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P336" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q336" t="inlineStr">
@@ -32447,12 +32842,12 @@
       </c>
       <c r="O337" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme CHPS</t>
+          <t>Eshiem CHPS</t>
         </is>
       </c>
       <c r="P337" t="inlineStr">
         <is>
-          <t>Gomoa Enyeme</t>
+          <t>Eshiem</t>
         </is>
       </c>
       <c r="Q337" t="inlineStr">
@@ -32596,6 +32991,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC338" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD338" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -32686,6 +33086,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC339" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD339" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -32776,6 +33181,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC340" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD340" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -32866,6 +33276,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC341" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD341" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -32956,6 +33371,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC342" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD342" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33046,6 +33466,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC343" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD343" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33136,6 +33561,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC344" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD344" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33226,6 +33656,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC345" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD345" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33316,6 +33751,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC346" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD346" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33406,6 +33846,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC347" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD347" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33496,6 +33941,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC348" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD348" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33581,6 +34031,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC349" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD349" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33671,6 +34126,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC350" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD350" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33761,6 +34221,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC351" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD351" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33846,6 +34311,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC352" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD352" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -33936,6 +34406,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC353" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD353" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -34026,6 +34501,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC354" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD354" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -34116,6 +34596,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC355" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD355" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -34206,6 +34691,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC356" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD356" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -34296,6 +34786,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC357" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD357" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -45880,7 +46375,7 @@
       </c>
       <c r="AB478" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AC478" t="inlineStr">
@@ -56491,6 +56986,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="W588" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
       <c r="X588">
         <v>29</v>
       </c>
@@ -61432,6 +61932,11 @@
           <t>0240533048</t>
         </is>
       </c>
+      <c r="V640" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W640" t="inlineStr">
         <is>
           <t>Male</t>
@@ -61912,6 +62417,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="W645" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
       <c r="X645">
         <v>57</v>
       </c>
@@ -66904,7 +67414,7 @@
       </c>
       <c r="AB697" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC697" t="inlineStr">
@@ -68550,7 +69060,7 @@
       </c>
       <c r="AB714" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Positive</t>
         </is>
       </c>
       <c r="AC714" t="inlineStr">
@@ -74648,7 +75158,7 @@
       </c>
       <c r="AB777" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC777" t="inlineStr">
@@ -76953,6 +77463,21 @@
       <c r="X801">
         <v>43</v>
       </c>
+      <c r="Y801" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA801" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AC801" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD801" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -78865,7 +79390,7 @@
       </c>
       <c r="AB821" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC821" t="inlineStr">
@@ -78963,7 +79488,7 @@
       </c>
       <c r="AB822" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC822" t="inlineStr">
@@ -80511,7 +81036,7 @@
       </c>
       <c r="AB838" t="inlineStr">
         <is>
-          <t>Positive</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="AC838" t="inlineStr">
@@ -80803,6 +81328,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC841" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD841" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -80891,6 +81421,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC842" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD842" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -80979,6 +81514,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC843" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD843" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81067,6 +81607,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC844" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD844" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81155,6 +81700,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC845" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD845" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81243,6 +81793,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC846" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD846" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81336,6 +81891,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC847" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD847" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81424,6 +81984,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC848" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD848" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81517,6 +82082,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC849" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD849" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81605,6 +82175,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC850" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD850" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81693,6 +82268,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC851" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD851" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81786,6 +82366,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC852" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD852" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81874,6 +82459,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC853" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD853" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -81962,6 +82552,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC854" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD854" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -82017,6 +82612,11 @@
           <t>BENYADZE</t>
         </is>
       </c>
+      <c r="V855" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="W855" t="inlineStr">
         <is>
           <t>Female</t>
@@ -82045,6 +82645,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC855" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD855" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -82133,6 +82738,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC856" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD856" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -82221,6 +82831,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC857" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD857" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -82314,6 +82929,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC858" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD858" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -82402,6 +83022,11 @@
           <t>Negative</t>
         </is>
       </c>
+      <c r="AC859" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
       <c r="AD859" t="inlineStr">
         <is>
           <t>Complete</t>
@@ -82488,6 +83113,11 @@
       <c r="AB860" t="inlineStr">
         <is>
           <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC860" t="inlineStr">
+        <is>
+          <t>No</t>
         </is>
       </c>
       <c r="AD860" t="inlineStr">

--- a/LF_study.xlsx
+++ b/LF_study.xlsx
@@ -2688,6 +2688,11 @@
           <t>Yes</t>
         </is>
       </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
       <c r="AC23" t="inlineStr">
         <is>
           <t>No</t>

--- a/LF_study.xlsx
+++ b/LF_study.xlsx
@@ -355,7 +355,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AL901"/>
+  <dimension ref="A1:AL966"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="18" max="18" width="20.7109375" style="2" customWidth="1"/>
@@ -87086,6 +87086,6261 @@
         </is>
       </c>
     </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="K902" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L902" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M902" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N902" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q902" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R902" s="2">
+        <v>46139</v>
+      </c>
+      <c r="S902" t="inlineStr">
+        <is>
+          <t>KYS 01</t>
+        </is>
+      </c>
+      <c r="T902" t="inlineStr">
+        <is>
+          <t>ABROBIAN0</t>
+        </is>
+      </c>
+      <c r="U902" t="inlineStr">
+        <is>
+          <t>0243021346</t>
+        </is>
+      </c>
+      <c r="V902" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W902" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X902">
+        <v>41</v>
+      </c>
+      <c r="Y902" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z902" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA902" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB902" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC902" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD902" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL902" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>902</t>
+        </is>
+      </c>
+      <c r="K903" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L903" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M903" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N903" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q903" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R903" s="2">
+        <v>46139</v>
+      </c>
+      <c r="S903" t="inlineStr">
+        <is>
+          <t>KYS 02</t>
+        </is>
+      </c>
+      <c r="U903" t="inlineStr">
+        <is>
+          <t>0257852973</t>
+        </is>
+      </c>
+      <c r="V903" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W903" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X903">
+        <v>26</v>
+      </c>
+      <c r="Y903" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z903" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA903" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB903" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC903" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD903" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL903" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>903</t>
+        </is>
+      </c>
+      <c r="K904" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L904" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M904" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N904" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q904" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R904" s="2">
+        <v>46139</v>
+      </c>
+      <c r="S904" t="inlineStr">
+        <is>
+          <t>KYS 03</t>
+        </is>
+      </c>
+      <c r="T904" t="inlineStr">
+        <is>
+          <t>EBUKROM</t>
+        </is>
+      </c>
+      <c r="V904" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W904" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X904">
+        <v>80</v>
+      </c>
+      <c r="Y904" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AA904" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB904" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC904" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD904" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL904" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>904</t>
+        </is>
+      </c>
+      <c r="K905" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L905" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M905" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N905" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q905" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R905" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S905" t="inlineStr">
+        <is>
+          <t>KYS 04</t>
+        </is>
+      </c>
+      <c r="T905" t="inlineStr">
+        <is>
+          <t>SCHOOL</t>
+        </is>
+      </c>
+      <c r="V905" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W905" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X905">
+        <v>16</v>
+      </c>
+      <c r="Y905" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z905" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA905" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB905" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC905" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD905" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL905" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>905</t>
+        </is>
+      </c>
+      <c r="K906" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L906" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M906" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N906" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q906" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R906" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S906" t="inlineStr">
+        <is>
+          <t>KYS 05</t>
+        </is>
+      </c>
+      <c r="T906" t="inlineStr">
+        <is>
+          <t>KISSI</t>
+        </is>
+      </c>
+      <c r="U906" t="inlineStr">
+        <is>
+          <t>0246430364</t>
+        </is>
+      </c>
+      <c r="V906" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W906" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X906">
+        <v>27</v>
+      </c>
+      <c r="Y906" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z906" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA906" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB906" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC906" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD906" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL906" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>906</t>
+        </is>
+      </c>
+      <c r="K907" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L907" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M907" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N907" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q907" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R907" s="2">
+        <v>46149</v>
+      </c>
+      <c r="S907" t="inlineStr">
+        <is>
+          <t>KYS 06</t>
+        </is>
+      </c>
+      <c r="T907" t="inlineStr">
+        <is>
+          <t>SEFWI</t>
+        </is>
+      </c>
+      <c r="V907" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W907" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X907">
+        <v>60</v>
+      </c>
+      <c r="Y907" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z907" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA907" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB907" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC907" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD907" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL907" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>907</t>
+        </is>
+      </c>
+      <c r="K908" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L908" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M908" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N908" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q908" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R908" s="2">
+        <v>46154</v>
+      </c>
+      <c r="S908" t="inlineStr">
+        <is>
+          <t>KYS 07</t>
+        </is>
+      </c>
+      <c r="T908" t="inlineStr">
+        <is>
+          <t>KISSI</t>
+        </is>
+      </c>
+      <c r="U908" t="inlineStr">
+        <is>
+          <t>0530872652</t>
+        </is>
+      </c>
+      <c r="V908" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W908" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X908">
+        <v>17</v>
+      </c>
+      <c r="Y908" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z908" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA908" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB908" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC908" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD908" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL908" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>908</t>
+        </is>
+      </c>
+      <c r="K909" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L909" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M909" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N909" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q909" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R909" s="2">
+        <v>46154</v>
+      </c>
+      <c r="S909" t="inlineStr">
+        <is>
+          <t>KYS 08</t>
+        </is>
+      </c>
+      <c r="T909" t="inlineStr">
+        <is>
+          <t>KISSI</t>
+        </is>
+      </c>
+      <c r="U909" t="inlineStr">
+        <is>
+          <t>0591140212</t>
+        </is>
+      </c>
+      <c r="V909" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W909" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X909">
+        <v>28</v>
+      </c>
+      <c r="Y909" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z909" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA909" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB909" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC909" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD909" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL909" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>909</t>
+        </is>
+      </c>
+      <c r="K910" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L910" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M910" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N910" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q910" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R910" s="2">
+        <v>46154</v>
+      </c>
+      <c r="S910" t="inlineStr">
+        <is>
+          <t>KYS 09</t>
+        </is>
+      </c>
+      <c r="T910" t="inlineStr">
+        <is>
+          <t>KYIASE</t>
+        </is>
+      </c>
+      <c r="U910" t="inlineStr">
+        <is>
+          <t>0244152498</t>
+        </is>
+      </c>
+      <c r="V910" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W910" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X910">
+        <v>37</v>
+      </c>
+      <c r="Y910" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z910" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA910" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB910" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC910" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD910" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL910" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="K911" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L911" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M911" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N911" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q911" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R911" s="2">
+        <v>46156</v>
+      </c>
+      <c r="S911" t="inlineStr">
+        <is>
+          <t>KYS 10</t>
+        </is>
+      </c>
+      <c r="T911" t="inlineStr">
+        <is>
+          <t>KISSI</t>
+        </is>
+      </c>
+      <c r="U911" t="inlineStr">
+        <is>
+          <t>0550980739</t>
+        </is>
+      </c>
+      <c r="V911" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W911" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X911">
+        <v>20</v>
+      </c>
+      <c r="Y911" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z911" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA911" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB911" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC911" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD911" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL911" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>911</t>
+        </is>
+      </c>
+      <c r="K912" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L912" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M912" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N912" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q912" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R912" s="2">
+        <v>46156</v>
+      </c>
+      <c r="S912" t="inlineStr">
+        <is>
+          <t>KYS 11</t>
+        </is>
+      </c>
+      <c r="T912" t="inlineStr">
+        <is>
+          <t>KYIASE</t>
+        </is>
+      </c>
+      <c r="U912" t="inlineStr">
+        <is>
+          <t>0246829607</t>
+        </is>
+      </c>
+      <c r="V912" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W912" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X912">
+        <v>30</v>
+      </c>
+      <c r="Y912" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z912" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA912" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB912" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC912" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD912" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL912" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>912</t>
+        </is>
+      </c>
+      <c r="K913" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L913" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M913" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N913" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q913" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R913" s="2">
+        <v>46156</v>
+      </c>
+      <c r="S913" t="inlineStr">
+        <is>
+          <t>KYS 12</t>
+        </is>
+      </c>
+      <c r="T913" t="inlineStr">
+        <is>
+          <t>KYIASE</t>
+        </is>
+      </c>
+      <c r="U913" t="inlineStr">
+        <is>
+          <t>0534892673</t>
+        </is>
+      </c>
+      <c r="V913" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W913" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X913">
+        <v>27</v>
+      </c>
+      <c r="Y913" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z913" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA913" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB913" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC913" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD913" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL913" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>913</t>
+        </is>
+      </c>
+      <c r="K914" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L914" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M914" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N914" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q914" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R914" s="2">
+        <v>46163</v>
+      </c>
+      <c r="S914" t="inlineStr">
+        <is>
+          <t>KYS 13</t>
+        </is>
+      </c>
+      <c r="T914" t="inlineStr">
+        <is>
+          <t>KYIASE</t>
+        </is>
+      </c>
+      <c r="U914" t="inlineStr">
+        <is>
+          <t>0534404839</t>
+        </is>
+      </c>
+      <c r="V914" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W914" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X914">
+        <v>50</v>
+      </c>
+      <c r="Y914" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z914" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA914" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB914" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC914" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD914" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL914" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>914</t>
+        </is>
+      </c>
+      <c r="K915" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L915" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M915" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N915" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q915" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R915" s="2">
+        <v>46169</v>
+      </c>
+      <c r="S915" t="inlineStr">
+        <is>
+          <t>KYS 14</t>
+        </is>
+      </c>
+      <c r="T915" t="inlineStr">
+        <is>
+          <t>KYIASE</t>
+        </is>
+      </c>
+      <c r="U915" t="inlineStr">
+        <is>
+          <t>0537597012</t>
+        </is>
+      </c>
+      <c r="V915" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W915" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X915">
+        <v>32</v>
+      </c>
+      <c r="Y915" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z915" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA915" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB915" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC915" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD915" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL915" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>915</t>
+        </is>
+      </c>
+      <c r="K916" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L916" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M916" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N916" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q916" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R916" s="2">
+        <v>46169</v>
+      </c>
+      <c r="S916" t="inlineStr">
+        <is>
+          <t>KYS 15</t>
+        </is>
+      </c>
+      <c r="T916" t="inlineStr">
+        <is>
+          <t>KYIASE</t>
+        </is>
+      </c>
+      <c r="U916" t="inlineStr">
+        <is>
+          <t>0540443407</t>
+        </is>
+      </c>
+      <c r="V916" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W916" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X916">
+        <v>34</v>
+      </c>
+      <c r="Y916" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z916" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA916" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB916" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC916" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD916" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL916" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M917" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q917" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R917" s="2">
+        <v>46169</v>
+      </c>
+      <c r="S917" t="inlineStr">
+        <is>
+          <t>KYS 16</t>
+        </is>
+      </c>
+      <c r="T917" t="inlineStr">
+        <is>
+          <t>KYIASE</t>
+        </is>
+      </c>
+      <c r="U917" t="inlineStr">
+        <is>
+          <t>0539008536</t>
+        </is>
+      </c>
+      <c r="V917" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W917" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X917">
+        <v>36</v>
+      </c>
+      <c r="Y917" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z917" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA917" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB917" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC917" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD917" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL917" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>917</t>
+        </is>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M918" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q918" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R918" s="2">
+        <v>46169</v>
+      </c>
+      <c r="S918" t="inlineStr">
+        <is>
+          <t>KYS 17</t>
+        </is>
+      </c>
+      <c r="T918" t="inlineStr">
+        <is>
+          <t>KYIASE</t>
+        </is>
+      </c>
+      <c r="U918" t="inlineStr">
+        <is>
+          <t>0539008536</t>
+        </is>
+      </c>
+      <c r="V918" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W918" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X918">
+        <v>35</v>
+      </c>
+      <c r="Y918" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z918" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA918" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB918" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC918" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD918" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL918" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>918</t>
+        </is>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M919" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q919" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R919" s="2">
+        <v>46169</v>
+      </c>
+      <c r="S919" t="inlineStr">
+        <is>
+          <t>KYS 18</t>
+        </is>
+      </c>
+      <c r="T919" t="inlineStr">
+        <is>
+          <t>ANTADO</t>
+        </is>
+      </c>
+      <c r="V919" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W919" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X919">
+        <v>6</v>
+      </c>
+      <c r="Y919" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z919" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA919" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB919" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC919" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD919" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL919" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M920" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q920" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R920" s="2">
+        <v>46164</v>
+      </c>
+      <c r="S920" t="inlineStr">
+        <is>
+          <t>KYS19</t>
+        </is>
+      </c>
+      <c r="T920" t="inlineStr">
+        <is>
+          <t>Biseadze</t>
+        </is>
+      </c>
+      <c r="V920" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W920" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X920">
+        <v>40</v>
+      </c>
+      <c r="Y920" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z920" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA920" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB920" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC920" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD920" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL920" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M921" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q921" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R921" s="2">
+        <v>46168</v>
+      </c>
+      <c r="S921" t="inlineStr">
+        <is>
+          <t>KYS 20</t>
+        </is>
+      </c>
+      <c r="T921" t="inlineStr">
+        <is>
+          <t>KISSI</t>
+        </is>
+      </c>
+      <c r="V921" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W921" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X921">
+        <v>22</v>
+      </c>
+      <c r="Y921" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z921" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA921" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB921" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC921" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD921" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL921" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>921</t>
+        </is>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M922" t="inlineStr">
+        <is>
+          <t>Kyiase CHPS</t>
+        </is>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>Kyiase</t>
+        </is>
+      </c>
+      <c r="Q922" t="inlineStr">
+        <is>
+          <t>OPHELIA DEBRAH</t>
+        </is>
+      </c>
+      <c r="R922" s="2">
+        <v>46164</v>
+      </c>
+      <c r="S922" t="inlineStr">
+        <is>
+          <t>KYS 21</t>
+        </is>
+      </c>
+      <c r="T922" t="inlineStr">
+        <is>
+          <t>ANTADO</t>
+        </is>
+      </c>
+      <c r="V922" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W922" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X922">
+        <v>5</v>
+      </c>
+      <c r="Y922" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z922" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA922" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB922" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC922" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD922" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL922" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>922</t>
+        </is>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M923" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q923" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R923" s="2">
+        <v>46137</v>
+      </c>
+      <c r="S923" t="inlineStr">
+        <is>
+          <t>ANT 18</t>
+        </is>
+      </c>
+      <c r="T923" t="inlineStr">
+        <is>
+          <t>KUMASI</t>
+        </is>
+      </c>
+      <c r="U923" t="inlineStr">
+        <is>
+          <t>0531603119</t>
+        </is>
+      </c>
+      <c r="V923" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W923" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X923">
+        <v>45</v>
+      </c>
+      <c r="Y923" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z923" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA923" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB923" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC923" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD923" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL923" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>923</t>
+        </is>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M924" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q924" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R924" s="2">
+        <v>46138</v>
+      </c>
+      <c r="S924" t="inlineStr">
+        <is>
+          <t>ANT 19</t>
+        </is>
+      </c>
+      <c r="T924" t="inlineStr">
+        <is>
+          <t>EGYAKWATA</t>
+        </is>
+      </c>
+      <c r="U924" t="inlineStr">
+        <is>
+          <t>0550294958</t>
+        </is>
+      </c>
+      <c r="V924" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W924" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X924">
+        <v>5</v>
+      </c>
+      <c r="Y924" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z924" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA924" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB924" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC924" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD924" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL924" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>924</t>
+        </is>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M925" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q925" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R925" s="2">
+        <v>46138</v>
+      </c>
+      <c r="S925" t="inlineStr">
+        <is>
+          <t>ANT 20</t>
+        </is>
+      </c>
+      <c r="T925" t="inlineStr">
+        <is>
+          <t>EGYAKWATA</t>
+        </is>
+      </c>
+      <c r="U925" t="inlineStr">
+        <is>
+          <t>0249123342</t>
+        </is>
+      </c>
+      <c r="V925" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W925" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X925">
+        <v>6</v>
+      </c>
+      <c r="Y925" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z925" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA925" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB925" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC925" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD925" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL925" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>925</t>
+        </is>
+      </c>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M926" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q926" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R926" s="2">
+        <v>46182</v>
+      </c>
+      <c r="S926" t="inlineStr">
+        <is>
+          <t>ANT 21</t>
+        </is>
+      </c>
+      <c r="T926" t="inlineStr">
+        <is>
+          <t>ABROAD</t>
+        </is>
+      </c>
+      <c r="V926" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W926" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X926">
+        <v>68</v>
+      </c>
+      <c r="Y926" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z926" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA926" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB926" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC926" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD926" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL926" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>926</t>
+        </is>
+      </c>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M927" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q927" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R927" s="2">
+        <v>46142</v>
+      </c>
+      <c r="S927" t="inlineStr">
+        <is>
+          <t>ANT 22</t>
+        </is>
+      </c>
+      <c r="T927" t="inlineStr">
+        <is>
+          <t>KOMFOKROM</t>
+        </is>
+      </c>
+      <c r="U927" t="inlineStr">
+        <is>
+          <t>0203397311</t>
+        </is>
+      </c>
+      <c r="V927" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W927" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X927">
+        <v>49</v>
+      </c>
+      <c r="Y927" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z927" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA927" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB927" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC927" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD927" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL927" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>927</t>
+        </is>
+      </c>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M928" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q928" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R928" s="2">
+        <v>46142</v>
+      </c>
+      <c r="S928" t="inlineStr">
+        <is>
+          <t>ANT 23</t>
+        </is>
+      </c>
+      <c r="T928" t="inlineStr">
+        <is>
+          <t>EGYAKWATA</t>
+        </is>
+      </c>
+      <c r="U928" t="inlineStr">
+        <is>
+          <t>0547033596</t>
+        </is>
+      </c>
+      <c r="V928" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W928" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X928">
+        <v>11</v>
+      </c>
+      <c r="Y928" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z928" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA928" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB928" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC928" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD928" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL928" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>928</t>
+        </is>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M929" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q929" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R929" s="2">
+        <v>46142</v>
+      </c>
+      <c r="S929" t="inlineStr">
+        <is>
+          <t>ANT 24</t>
+        </is>
+      </c>
+      <c r="T929" t="inlineStr">
+        <is>
+          <t>ANTSEAMBUA</t>
+        </is>
+      </c>
+      <c r="U929" t="inlineStr">
+        <is>
+          <t>0593605732</t>
+        </is>
+      </c>
+      <c r="V929" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W929" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X929">
+        <v>29</v>
+      </c>
+      <c r="Y929" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z929" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA929" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB929" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC929" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD929" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL929" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>929</t>
+        </is>
+      </c>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M930" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q930" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R930" s="2">
+        <v>46152</v>
+      </c>
+      <c r="S930" t="inlineStr">
+        <is>
+          <t>ANT 25</t>
+        </is>
+      </c>
+      <c r="T930" t="inlineStr">
+        <is>
+          <t>ABROAD</t>
+        </is>
+      </c>
+      <c r="U930" t="inlineStr">
+        <is>
+          <t>0534248743</t>
+        </is>
+      </c>
+      <c r="V930" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W930" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X930">
+        <v>5</v>
+      </c>
+      <c r="Y930" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z930" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA930" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB930" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC930" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD930" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL930" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M931" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q931" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R931" s="2">
+        <v>46152</v>
+      </c>
+      <c r="S931" t="inlineStr">
+        <is>
+          <t>ANT 26</t>
+        </is>
+      </c>
+      <c r="T931" t="inlineStr">
+        <is>
+          <t>ANWEAMU</t>
+        </is>
+      </c>
+      <c r="U931" t="inlineStr">
+        <is>
+          <t>0248485955</t>
+        </is>
+      </c>
+      <c r="V931" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W931" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X931">
+        <v>29</v>
+      </c>
+      <c r="Y931" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z931" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA931" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB931" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC931" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD931" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL931" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>931</t>
+        </is>
+      </c>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M932" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q932" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R932" s="2">
+        <v>46152</v>
+      </c>
+      <c r="S932" t="inlineStr">
+        <is>
+          <t>ANT 27</t>
+        </is>
+      </c>
+      <c r="T932" t="inlineStr">
+        <is>
+          <t>ANTSEAMBUA</t>
+        </is>
+      </c>
+      <c r="U932" t="inlineStr">
+        <is>
+          <t>0547775269</t>
+        </is>
+      </c>
+      <c r="V932" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W932" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X932">
+        <v>25</v>
+      </c>
+      <c r="Y932" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z932" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA932" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB932" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC932" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD932" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL932" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>932</t>
+        </is>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M933" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q933" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R933" s="2">
+        <v>46155</v>
+      </c>
+      <c r="S933" t="inlineStr">
+        <is>
+          <t>ANT 28</t>
+        </is>
+      </c>
+      <c r="T933" t="inlineStr">
+        <is>
+          <t>ABROAD</t>
+        </is>
+      </c>
+      <c r="U933" t="inlineStr">
+        <is>
+          <t>0593543232</t>
+        </is>
+      </c>
+      <c r="V933" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W933" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X933">
+        <v>29</v>
+      </c>
+      <c r="Y933" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z933" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA933" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB933" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC933" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD933" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL933" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>933</t>
+        </is>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M934" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q934" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R934" s="2">
+        <v>46161</v>
+      </c>
+      <c r="S934" t="inlineStr">
+        <is>
+          <t>ANT 29</t>
+        </is>
+      </c>
+      <c r="T934" t="inlineStr">
+        <is>
+          <t>EGYAKWATA</t>
+        </is>
+      </c>
+      <c r="U934" t="inlineStr">
+        <is>
+          <t>0595047600</t>
+        </is>
+      </c>
+      <c r="V934" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W934" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X934">
+        <v>20</v>
+      </c>
+      <c r="Y934" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z934" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA934" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB934" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC934" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD934" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL934" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>934</t>
+        </is>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M935" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q935" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R935" s="2">
+        <v>46162</v>
+      </c>
+      <c r="S935" t="inlineStr">
+        <is>
+          <t>ANT 30</t>
+        </is>
+      </c>
+      <c r="T935" t="inlineStr">
+        <is>
+          <t>KWANTA</t>
+        </is>
+      </c>
+      <c r="U935" t="inlineStr">
+        <is>
+          <t>0544772687</t>
+        </is>
+      </c>
+      <c r="V935" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W935" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X935">
+        <v>55</v>
+      </c>
+      <c r="Y935" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z935" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA935" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB935" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC935" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD935" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL935" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M936" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q936" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R936" s="2">
+        <v>46162</v>
+      </c>
+      <c r="S936" t="inlineStr">
+        <is>
+          <t>ANT 31</t>
+        </is>
+      </c>
+      <c r="T936" t="inlineStr">
+        <is>
+          <t>KUMASI</t>
+        </is>
+      </c>
+      <c r="U936" t="inlineStr">
+        <is>
+          <t>0530749830</t>
+        </is>
+      </c>
+      <c r="V936" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W936" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X936">
+        <v>13</v>
+      </c>
+      <c r="Y936" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z936" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA936" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB936" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC936" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD936" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL936" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>936</t>
+        </is>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M937" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q937" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R937" s="2">
+        <v>46163</v>
+      </c>
+      <c r="S937" t="inlineStr">
+        <is>
+          <t>ANT 32</t>
+        </is>
+      </c>
+      <c r="T937" t="inlineStr">
+        <is>
+          <t>APPIAHKROM</t>
+        </is>
+      </c>
+      <c r="U937" t="inlineStr">
+        <is>
+          <t>0593665910</t>
+        </is>
+      </c>
+      <c r="V937" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W937" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X937">
+        <v>42</v>
+      </c>
+      <c r="Y937" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z937" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA937" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB937" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC937" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD937" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL937" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>937</t>
+        </is>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M938" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q938" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R938" s="2">
+        <v>46163</v>
+      </c>
+      <c r="S938" t="inlineStr">
+        <is>
+          <t>ANT 33</t>
+        </is>
+      </c>
+      <c r="T938" t="inlineStr">
+        <is>
+          <t>KROFOFOMU</t>
+        </is>
+      </c>
+      <c r="U938" t="inlineStr">
+        <is>
+          <t>0207988519</t>
+        </is>
+      </c>
+      <c r="V938" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W938" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X938">
+        <v>18</v>
+      </c>
+      <c r="Y938" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z938" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA938" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB938" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC938" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD938" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL938" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>938</t>
+        </is>
+      </c>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M939" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q939" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R939" s="2">
+        <v>46167</v>
+      </c>
+      <c r="S939" t="inlineStr">
+        <is>
+          <t>ANT 34</t>
+        </is>
+      </c>
+      <c r="T939" t="inlineStr">
+        <is>
+          <t>ABROAD</t>
+        </is>
+      </c>
+      <c r="U939" t="inlineStr">
+        <is>
+          <t>0555858411</t>
+        </is>
+      </c>
+      <c r="V939" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W939" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X939">
+        <v>26</v>
+      </c>
+      <c r="Y939" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z939" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA939" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB939" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC939" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD939" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL939" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>939</t>
+        </is>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M940" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q940" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R940" s="2">
+        <v>46168</v>
+      </c>
+      <c r="S940" t="inlineStr">
+        <is>
+          <t>ANT 35</t>
+        </is>
+      </c>
+      <c r="T940" t="inlineStr">
+        <is>
+          <t>ANWEAMU</t>
+        </is>
+      </c>
+      <c r="U940" t="inlineStr">
+        <is>
+          <t>0274795914</t>
+        </is>
+      </c>
+      <c r="V940" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W940" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X940">
+        <v>55</v>
+      </c>
+      <c r="Y940" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z940" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA940" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB940" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC940" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD940" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL940" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>940</t>
+        </is>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M941" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q941" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R941" s="2">
+        <v>46168</v>
+      </c>
+      <c r="S941" t="inlineStr">
+        <is>
+          <t>ANT 36</t>
+        </is>
+      </c>
+      <c r="T941" t="inlineStr">
+        <is>
+          <t>ANTSEAMBUA</t>
+        </is>
+      </c>
+      <c r="U941" t="inlineStr">
+        <is>
+          <t>0542116332</t>
+        </is>
+      </c>
+      <c r="V941" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W941" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X941">
+        <v>23</v>
+      </c>
+      <c r="Y941" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z941" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA941" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB941" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC941" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD941" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL941" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>941</t>
+        </is>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M942" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q942" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R942" s="2">
+        <v>46168</v>
+      </c>
+      <c r="S942" t="inlineStr">
+        <is>
+          <t>ANT 37</t>
+        </is>
+      </c>
+      <c r="U942" t="inlineStr">
+        <is>
+          <t>0596692228</t>
+        </is>
+      </c>
+      <c r="V942" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W942" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X942">
+        <v>33</v>
+      </c>
+      <c r="Y942" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z942" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA942" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB942" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC942" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD942" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL942" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>942</t>
+        </is>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M943" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q943" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R943" s="2">
+        <v>46168</v>
+      </c>
+      <c r="S943" t="inlineStr">
+        <is>
+          <t>ANT 38</t>
+        </is>
+      </c>
+      <c r="T943" t="inlineStr">
+        <is>
+          <t>KUMASI</t>
+        </is>
+      </c>
+      <c r="U943" t="inlineStr">
+        <is>
+          <t>0596527927</t>
+        </is>
+      </c>
+      <c r="V943" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W943" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X943">
+        <v>7</v>
+      </c>
+      <c r="Y943" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z943" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA943" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB943" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC943" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD943" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL943" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>943</t>
+        </is>
+      </c>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M944" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q944" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R944" s="2">
+        <v>46169</v>
+      </c>
+      <c r="S944" t="inlineStr">
+        <is>
+          <t>ANT 39</t>
+        </is>
+      </c>
+      <c r="T944" t="inlineStr">
+        <is>
+          <t>EGYAKWATA</t>
+        </is>
+      </c>
+      <c r="V944" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W944" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X944">
+        <v>6</v>
+      </c>
+      <c r="Y944" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z944" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA944" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB944" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC944" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD944" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL944" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>944</t>
+        </is>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M945" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q945" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R945" s="2">
+        <v>46170</v>
+      </c>
+      <c r="S945" t="inlineStr">
+        <is>
+          <t>ANT 40</t>
+        </is>
+      </c>
+      <c r="T945" t="inlineStr">
+        <is>
+          <t>ANWEAMU</t>
+        </is>
+      </c>
+      <c r="U945" t="inlineStr">
+        <is>
+          <t>0246920382</t>
+        </is>
+      </c>
+      <c r="V945" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W945" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X945">
+        <v>6</v>
+      </c>
+      <c r="Y945" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z945" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA945" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB945" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC945" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD945" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL945" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>945</t>
+        </is>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M946" t="inlineStr">
+        <is>
+          <t>Antsiambua CHPS</t>
+        </is>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>Antsiambua</t>
+        </is>
+      </c>
+      <c r="Q946" t="inlineStr">
+        <is>
+          <t>Agnes Odoom</t>
+        </is>
+      </c>
+      <c r="R946" s="2">
+        <v>46174</v>
+      </c>
+      <c r="S946" t="inlineStr">
+        <is>
+          <t>ANT 41</t>
+        </is>
+      </c>
+      <c r="T946" t="inlineStr">
+        <is>
+          <t>ESSUMANKROM</t>
+        </is>
+      </c>
+      <c r="U946" t="inlineStr">
+        <is>
+          <t>0204252367</t>
+        </is>
+      </c>
+      <c r="V946" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W946" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X946">
+        <v>12</v>
+      </c>
+      <c r="Y946" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z946" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA946" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB946" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC946" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD946" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL946" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M947" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q947" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R947" s="2">
+        <v>46138</v>
+      </c>
+      <c r="S947" t="inlineStr">
+        <is>
+          <t>ABE 01</t>
+        </is>
+      </c>
+      <c r="T947" t="inlineStr">
+        <is>
+          <t>DWABOR</t>
+        </is>
+      </c>
+      <c r="U947" t="inlineStr">
+        <is>
+          <t>024634061</t>
+        </is>
+      </c>
+      <c r="V947" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W947" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X947">
+        <v>32</v>
+      </c>
+      <c r="Y947" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z947" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA947" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB947" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC947" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD947" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL947" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M948" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q948" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R948" s="2">
+        <v>46140</v>
+      </c>
+      <c r="S948" t="inlineStr">
+        <is>
+          <t>ABE 02</t>
+        </is>
+      </c>
+      <c r="T948" t="inlineStr">
+        <is>
+          <t>AHIAFUL</t>
+        </is>
+      </c>
+      <c r="V948" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W948" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X948">
+        <v>8</v>
+      </c>
+      <c r="Y948" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z948" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA948" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB948" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC948" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD948" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL948" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>948</t>
+        </is>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M949" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q949" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R949" s="2">
+        <v>46141</v>
+      </c>
+      <c r="S949" t="inlineStr">
+        <is>
+          <t>ABE 03</t>
+        </is>
+      </c>
+      <c r="T949" t="inlineStr">
+        <is>
+          <t>AMARFUL</t>
+        </is>
+      </c>
+      <c r="U949" t="inlineStr">
+        <is>
+          <t>0256718409</t>
+        </is>
+      </c>
+      <c r="V949" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W949" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X949">
+        <v>24</v>
+      </c>
+      <c r="Y949" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z949" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA949" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB949" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC949" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD949" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL949" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M950" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q950" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R950" s="2">
+        <v>46143</v>
+      </c>
+      <c r="S950" t="inlineStr">
+        <is>
+          <t>ABE 04</t>
+        </is>
+      </c>
+      <c r="T950" t="inlineStr">
+        <is>
+          <t>DWABOR</t>
+        </is>
+      </c>
+      <c r="U950" t="inlineStr">
+        <is>
+          <t>0502427303</t>
+        </is>
+      </c>
+      <c r="V950" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W950" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X950">
+        <v>14</v>
+      </c>
+      <c r="Y950" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z950" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA950" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB950" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC950" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD950" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL950" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>950</t>
+        </is>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M951" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q951" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R951" s="2">
+        <v>46155</v>
+      </c>
+      <c r="S951" t="inlineStr">
+        <is>
+          <t>ABE 05</t>
+        </is>
+      </c>
+      <c r="T951" t="inlineStr">
+        <is>
+          <t>AYENSUDO</t>
+        </is>
+      </c>
+      <c r="U951" t="inlineStr">
+        <is>
+          <t>0556327604</t>
+        </is>
+      </c>
+      <c r="V951" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W951" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X951">
+        <v>18</v>
+      </c>
+      <c r="Y951" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z951" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA951" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB951" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC951" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD951" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL951" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>951</t>
+        </is>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M952" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q952" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R952" s="2">
+        <v>46157</v>
+      </c>
+      <c r="S952" t="inlineStr">
+        <is>
+          <t>ABE 06</t>
+        </is>
+      </c>
+      <c r="T952" t="inlineStr">
+        <is>
+          <t>ABEYEE</t>
+        </is>
+      </c>
+      <c r="U952" t="inlineStr">
+        <is>
+          <t>0242909674</t>
+        </is>
+      </c>
+      <c r="V952" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W952" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X952">
+        <v>33</v>
+      </c>
+      <c r="Y952" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z952" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA952" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB952" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC952" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD952" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL952" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>952</t>
+        </is>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M953" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q953" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R953" s="2">
+        <v>46157</v>
+      </c>
+      <c r="S953" t="inlineStr">
+        <is>
+          <t>ABE 07</t>
+        </is>
+      </c>
+      <c r="T953" t="inlineStr">
+        <is>
+          <t>KYIAHOMTSEW</t>
+        </is>
+      </c>
+      <c r="V953" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W953" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X953">
+        <v>15</v>
+      </c>
+      <c r="Y953" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z953" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA953" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB953" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC953" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD953" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL953" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>953</t>
+        </is>
+      </c>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M954" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q954" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R954" s="2">
+        <v>46159</v>
+      </c>
+      <c r="S954" t="inlineStr">
+        <is>
+          <t>ABE 08</t>
+        </is>
+      </c>
+      <c r="T954" t="inlineStr">
+        <is>
+          <t>NKASIA</t>
+        </is>
+      </c>
+      <c r="V954" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W954" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X954">
+        <v>6</v>
+      </c>
+      <c r="Y954" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z954" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA954" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB954" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC954" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD954" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL954" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>954</t>
+        </is>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M955" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q955" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R955" s="2">
+        <v>46159</v>
+      </c>
+      <c r="S955" t="inlineStr">
+        <is>
+          <t>ABE 09</t>
+        </is>
+      </c>
+      <c r="T955" t="inlineStr">
+        <is>
+          <t>NKASIA</t>
+        </is>
+      </c>
+      <c r="V955" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W955" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X955">
+        <v>7</v>
+      </c>
+      <c r="Y955" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z955" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA955" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB955" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC955" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD955" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL955" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>955</t>
+        </is>
+      </c>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M956" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q956" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R956" s="2">
+        <v>46159</v>
+      </c>
+      <c r="S956" t="inlineStr">
+        <is>
+          <t>ABE 10</t>
+        </is>
+      </c>
+      <c r="T956" t="inlineStr">
+        <is>
+          <t>DW</t>
+        </is>
+      </c>
+      <c r="V956" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W956" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X956">
+        <v>18</v>
+      </c>
+      <c r="Y956" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z956" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA956" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB956" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC956" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD956" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL956" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>956</t>
+        </is>
+      </c>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M957" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q957" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R957" s="2">
+        <v>46128</v>
+      </c>
+      <c r="S957" t="inlineStr">
+        <is>
+          <t>ABE 11</t>
+        </is>
+      </c>
+      <c r="T957" t="inlineStr">
+        <is>
+          <t>WOREBEBA</t>
+        </is>
+      </c>
+      <c r="V957" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W957" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X957">
+        <v>21</v>
+      </c>
+      <c r="Y957" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z957" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA957" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB957" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC957" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD957" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL957" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>957</t>
+        </is>
+      </c>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M958" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q958" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R958" s="2">
+        <v>46128</v>
+      </c>
+      <c r="S958" t="inlineStr">
+        <is>
+          <t>ABE 12</t>
+        </is>
+      </c>
+      <c r="T958" t="inlineStr">
+        <is>
+          <t>AMARFUL</t>
+        </is>
+      </c>
+      <c r="V958" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W958" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X958">
+        <v>20</v>
+      </c>
+      <c r="Y958" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z958" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA958" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB958" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC958" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD958" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL958" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>958</t>
+        </is>
+      </c>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M959" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q959" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R959" s="2">
+        <v>46156</v>
+      </c>
+      <c r="S959" t="inlineStr">
+        <is>
+          <t>ABE 13</t>
+        </is>
+      </c>
+      <c r="T959" t="inlineStr">
+        <is>
+          <t>GHOTTO</t>
+        </is>
+      </c>
+      <c r="V959" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W959" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X959">
+        <v>57</v>
+      </c>
+      <c r="Y959" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z959" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA959" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB959" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC959" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD959" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL959" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>959</t>
+        </is>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M960" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q960" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R960" s="2">
+        <v>46158</v>
+      </c>
+      <c r="S960" t="inlineStr">
+        <is>
+          <t>ABE 14</t>
+        </is>
+      </c>
+      <c r="T960" t="inlineStr">
+        <is>
+          <t>DWABOR</t>
+        </is>
+      </c>
+      <c r="V960" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W960" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X960">
+        <v>66</v>
+      </c>
+      <c r="Y960" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z960" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA960" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB960" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC960" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD960" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL960" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>960</t>
+        </is>
+      </c>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M961" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q961" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R961" s="2">
+        <v>46154</v>
+      </c>
+      <c r="S961" t="inlineStr">
+        <is>
+          <t>ABE 15</t>
+        </is>
+      </c>
+      <c r="T961" t="inlineStr">
+        <is>
+          <t>GHOTTO</t>
+        </is>
+      </c>
+      <c r="V961" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W961" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X961">
+        <v>12</v>
+      </c>
+      <c r="Y961" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z961" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA961" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB961" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC961" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD961" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL961" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>961</t>
+        </is>
+      </c>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M962" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q962" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R962" s="2">
+        <v>46159</v>
+      </c>
+      <c r="S962" t="inlineStr">
+        <is>
+          <t>ABE 16</t>
+        </is>
+      </c>
+      <c r="T962" t="inlineStr">
+        <is>
+          <t>GHOTTO</t>
+        </is>
+      </c>
+      <c r="U962" t="inlineStr">
+        <is>
+          <t>0276642992</t>
+        </is>
+      </c>
+      <c r="V962" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W962" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X962">
+        <v>24</v>
+      </c>
+      <c r="Y962" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z962" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA962" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB962" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC962" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD962" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL962" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>962</t>
+        </is>
+      </c>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M963" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q963" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R963" s="2">
+        <v>46159</v>
+      </c>
+      <c r="S963" t="inlineStr">
+        <is>
+          <t>ABE 17</t>
+        </is>
+      </c>
+      <c r="T963" t="inlineStr">
+        <is>
+          <t>ABEYEE</t>
+        </is>
+      </c>
+      <c r="U963" t="inlineStr">
+        <is>
+          <t>0556144868</t>
+        </is>
+      </c>
+      <c r="V963" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W963" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X963">
+        <v>27</v>
+      </c>
+      <c r="Y963" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z963" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA963" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB963" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC963" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD963" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL963" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>963</t>
+        </is>
+      </c>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M964" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q964" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R964" s="2">
+        <v>46159</v>
+      </c>
+      <c r="S964" t="inlineStr">
+        <is>
+          <t>ABE 18</t>
+        </is>
+      </c>
+      <c r="T964" t="inlineStr">
+        <is>
+          <t>GHOTTO</t>
+        </is>
+      </c>
+      <c r="U964" t="inlineStr">
+        <is>
+          <t>056642992</t>
+        </is>
+      </c>
+      <c r="V964" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W964" t="inlineStr">
+        <is>
+          <t>Female</t>
+        </is>
+      </c>
+      <c r="X964">
+        <v>59</v>
+      </c>
+      <c r="Y964" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z964" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AA964" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB964" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC964" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD964" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL964" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>964</t>
+        </is>
+      </c>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M965" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q965" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R965" s="2">
+        <v>46159</v>
+      </c>
+      <c r="S965" t="inlineStr">
+        <is>
+          <t>ABE 19</t>
+        </is>
+      </c>
+      <c r="T965" t="inlineStr">
+        <is>
+          <t>AMARFUL</t>
+        </is>
+      </c>
+      <c r="U965" t="inlineStr">
+        <is>
+          <t>024189935</t>
+        </is>
+      </c>
+      <c r="V965" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W965" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X965">
+        <v>26</v>
+      </c>
+      <c r="Y965" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z965" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA965" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB965" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="AC965" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD965" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL965" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>965</t>
+        </is>
+      </c>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>KEEA-Municipal</t>
+        </is>
+      </c>
+      <c r="M966" t="inlineStr">
+        <is>
+          <t>Abeyee CHPS</t>
+        </is>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>Abeyee</t>
+        </is>
+      </c>
+      <c r="Q966" t="inlineStr">
+        <is>
+          <t>ELIZABETH APPIAH</t>
+        </is>
+      </c>
+      <c r="R966" s="2">
+        <v>46161</v>
+      </c>
+      <c r="S966" t="inlineStr">
+        <is>
+          <t>ABE 20</t>
+        </is>
+      </c>
+      <c r="T966" t="inlineStr">
+        <is>
+          <t>ABEYEE</t>
+        </is>
+      </c>
+      <c r="V966" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="W966" t="inlineStr">
+        <is>
+          <t>Male</t>
+        </is>
+      </c>
+      <c r="X966">
+        <v>42</v>
+      </c>
+      <c r="Y966" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="Z966" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AA966" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="AB966" t="inlineStr">
+        <is>
+          <t>Positive</t>
+        </is>
+      </c>
+      <c r="AC966" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="AD966" t="inlineStr">
+        <is>
+          <t>Complete</t>
+        </is>
+      </c>
+      <c r="AL966" t="inlineStr">
+        <is>
+          <t>Incomplete</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
